--- a/VERIF/sram_verif/sram_top_test_plan.xlsx
+++ b/VERIF/sram_verif/sram_top_test_plan.xlsx
@@ -1454,14 +1454,16 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Burst crossing end of SRAM</t>
+          <t>Bursts at the end of the SRAM window</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1. Issue INCR write/read of 4 beats starting at 0x107F_FFE0.
-2. Verify in-range beats complete, out-of-range beats are suppressed and response = DECERR.
-3. Verify no address aliasing to word 0.</t>
+          <t>1. Note: an INCR burst must not cross a 4 KB boundary (AXI A3.4.1), and the SRAM window starts and ends on 4 KB boundaries (0x1070_0000 / 0x1080_0000), so no legal INCR burst can run from in-range into out-of-range. A 4-beat 16 B INCR from 0x107F_FFE0 is therefore illegal and not used.
+2. Issue a 4-beat 16 B INCR write/read starting at 0x107F_FFC0 (last 4 words, ends at 0x107F_FFFF); verify OKAY on every beat and correct read data.
+3. Issue a 4-beat 16 B WRAP write/read starting at 0x107F_FFE0 (wraps inside 0x107F_FFC0-0x107F_FFFF); verify OKAY and the wrapped beat order.
+4. Issue a 4-beat INCR write starting at 0x1080_0000 (first out-of-range address); verify BRESP=DECERR and no SRAM write (multi-beat out-of-range read: see AXI_ADDR_006).
+5. Verify no address aliasing to word 0 (word 0 unchanged).</t>
         </is>
       </c>
       <c r="D37" s="3" t="n"/>
